--- a/Data/tracker_temperature.xlsx
+++ b/Data/tracker_temperature.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\Vicon (EPSURIS) Main\Public Files\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F278F41E-2CD8-4ACC-B85C-2A2F9AEC6BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F903CBCE-DEC5-4F3F-95A7-5D9E6F011813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
@@ -1332,6 +1332,9 @@
                   <c:v>46273</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1429,6 +1432,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>23.283333333333267</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0</c:v>
@@ -1743,6 +1749,9 @@
                   <c:v>46273</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1840,6 +1849,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13416,17 +13428,29 @@
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E397" s="6" t="str">
+      <c r="A397" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B397" s="9">
+        <v>0.86597222222222225</v>
+      </c>
+      <c r="C397" s="7">
+        <v>31</v>
+      </c>
+      <c r="D397" s="2">
+        <v>32</v>
+      </c>
+      <c r="E397" s="6">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="F397" s="2" t="str">
+        <v>2.9999999999999893</v>
+      </c>
+      <c r="F397" s="2">
         <f t="shared" si="13"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G397" s="9">
         <f>_xlfn.XLOOKUP(Log!A397, 'Daily Summary'!A:A, 'Daily Summary'!C:C, "TBD")</f>
-        <v>0</v>
+        <v>0.86388888888888893</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.3">
@@ -17464,7 +17488,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" cm="1">
-        <f t="array" ref="A2:A31">_xlfn.UNIQUE(Log!$A$3:$A$2488)</f>
+        <f t="array" ref="A2:A32">_xlfn.UNIQUE(Log!$A$3:$A$2488)</f>
         <v>46228</v>
       </c>
       <c r="B2" s="2">
@@ -17930,11 +17954,23 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B31" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0.86388888888888893</v>
+      </c>
+      <c r="D31" s="45">
+        <f>IF(C31="", "–", _xlfn.MINIFS(Log!$E$3:$E$1988, Log!$A$3:$A$1988, $A31, Log!$C$3:$C$1988,"&gt;=50"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
+      <c r="A32" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
